--- a/PMI-DZT2/ПМИ ЛО/pmi_lodzt/ss1_mode/СС_11.xlsx
+++ b/PMI-DZT2/ПМИ ЛО/pmi_lodzt/ss1_mode/СС_11.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,18 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -46,7 +58,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -60,16 +72,37 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,189 +472,189 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_genrbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_genrbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SGF3_genrbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SGF4_genrbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_hvcbptrc1_hvtcboff</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_lvcbptrc1_lvtprmcboff1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_lvcbrecrbre1_lvtprmcboff1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_lvcbptrc1_lvtprmcboff2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_lvcbrecrbre1_lvtprmcboff2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_tsa</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_tsa</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>SGF3_tsa</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>SGF4_tsa</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>SGF5_tsa</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>SGF6_tsa</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>SGF7_tsa</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>SGF8_tsa</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>SGF9_tsa</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>SGF10_tsa</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>SGF11_tsa</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>SGF12_tsa</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>SGF13_tsa</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_lvalh</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_lvalh</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>SGF3_lvalh</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>SGF4_lvalh</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>SGF5_lvalh</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>SGF6_lvalh</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>SGF7_lvalh</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>SGF8_lvalh</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>SGF9_lvalh</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>SGF10_lvalh</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>SGF11_lvalh</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>SGF12_lvalh</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>SGF13_lvalh</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_EnaDis</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_CurrentPickUp</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_ActUpSwitch</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_TypeOfCtrlCurrent</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_EnaDis</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>HVTCBOFF_1_HVCBPTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBPTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBRECRBRE1_EnaDis</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBPTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBRECRBRE1_EnaDis</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SA1</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SA2</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SA3</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SA4</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SG1</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SG2</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SG3</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_GAS_OCControl_SG1</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_TECH_OCControl_SG1</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_ARCnn1_OCControl</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_ARCnn2_OCControl</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_CBFPnn1_OCControl</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_CBFPnn2_OCControl</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_GASSign_Ctl</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_LowIsolGAS_Ctl</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_GASBlock_Ctl</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_TECHSign_Ctl</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_LowIsolTECH_Ctl</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_TECHBlock_Ctl</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_ALMSign_Ctl</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_OCSign_Ctl</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_OCnnSign_Ctl</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_OpExt_Ctl</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_CtlCir_Ctl</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_TestBlock_Ctl</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_ExtSignGen_Ctl</t>
         </is>
       </c>
     </row>
@@ -753,29 +786,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>T1_genrbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Iset_genrbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>T1_hvcbptrc1_hvtcboff</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>T1_lvcbptrc1_lvtprmcboff1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>T1_lvcbptrc1_lvtprmcboff2</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_Top</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_Iop</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>HVTCBOFF_1_HVCBPTRC1_Tpulse</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBPTRC1_Tpulse</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBPTRC1_Tpulse</t>
         </is>
       </c>
     </row>
@@ -851,192 +884,192 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VYVOD</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otkl_ot_so</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>OV_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>OV_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>OV_hvcbptrc1_hvtcboff</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otkl_zdz1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otkl_zdz2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otkl_urov1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otkl_urov2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvcbptrc1_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvcbrecrbre1_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvcbptrc1_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvcbrecrbre1_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>OV_rbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_urov_vnesh</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Polozh_SA1</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Polozh_SA2</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Polozh_SA3</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Polozh_SA4</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Polozh_SG1</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Polozh_SG2</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Polozh_SG3</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>ot_gz</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>ot_tz</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>ot_zdz_nn1</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>ot_zdz_nn2</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>ot_urov_nn1</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>ot_urov_nn2</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_sign1</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_sign2</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_sign3</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_sign4</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>DI_ControllerDisable</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>OpExtOfCoolSys</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TPRMOFFLVLGC</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TJNTPTRC</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>DI_JNTRBRE</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>DI_HVTCBOFF</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>OpExtOfARC_NN1</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>OpExtOfARC_NN2</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>OpExtOfCBFP_NN1</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>OpExtOfCBFP_NN2</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>DI_LVTPRMCBOFF1</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>DI_LVCBPTRC1</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>DI_LVCBRECRBRE1</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>DI_LVTPRMCBOFF2</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>DI_LVCBPTRC2</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>DI_LVCBRECRBRE2</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TPBRF</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>ExternalRBRFStart</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>CtlCirSwPos1</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>CtlCirSwPos2</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>CtlCirSwPos3</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>CtlCirSwPos4</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>TestBlockPos1</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>TestBlockPos2</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>TestBlockPos3</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>GAS_OCControl</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>TECH_OCControl</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>ARCnn1_OCControl</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>ARCnn2_OCControl</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>CBFPnn1_OCControl</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>CBFPnn2_OCControl</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>ExtSignal1</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>ExtSignal2</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>ExtSignal3</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>ExtSignal4</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>IA</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>IB</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" s="3" t="inlineStr">
         <is>
           <t>IC</t>
         </is>
@@ -1222,239 +1255,239 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>pusk_ptrc1_tprmofflvlgc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>srab_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>zapret_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_hvcbptrc1_hvtcboff</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_hvcbptrc1_hvtcboff</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>otkl_hvcbptrc1_hvtcboff</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>otkl_avar_hvcbptrc1_hvtcboff</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_lvcbptrc1_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_lvcbptrc1_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>otkl_lvcbptrc1_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>otkl_avar_lvcbptrc1_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_lvcbrecrbre1_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_lvcbrecrbre1_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>zapret_lvcbrecrbre1_lvtcboff1</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_lvcbptrc1_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_lvcbptrc1_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>otkl_lvcbptrc1_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>otkl_avar_lvcbptrc1_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_lvcbrecrbre1_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_lvcbrecrbre1_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>zapret_lvcbrecrbre1_lvtcboff2</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_rbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_rbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>srab_rbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_rbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>io_rbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>srab_na_sebya_rbrf1_tpbrf</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>SS_gz_sign</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>SS_gz_nizk_isol</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>SS_gz_zablok</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>SS_tz_sign</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>SS_tz_nizk_isol</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>SS_tz_zablok</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>SS_ts_sign</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>SS_vnesh_otkl</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>SS_vyh_zepi_razobr</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>SS_bi_vyved</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>SS_ot_sign</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>SS_neispr_ot_gz</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>SS_neispr_ot_tz</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>SS_ot_nn_sign</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>SS_obsh_vnesh_sign</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_lvalh</t>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_Op</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_BlkOp</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>HVTCBOFF_1_HVCBPTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>HVTCBOFF_1_HVCBPTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>HVTCBOFF_1_HVCBPTRC1_Op</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>HVTCBOFF_1_HVCBPTRC1_Tr</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBPTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBPTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBPTRC1_Op</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBPTRC1_Tr</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBRECRBRE1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBRECRBRE1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF1_1_LVCBRECRBRE1_BlkOp</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBPTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBPTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBPTRC1_Op</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBPTRC1_Tr</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBRECRBRE1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBRECRBRE1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>LVTPRMCBOFF2_1_LVCBRECRBRE1_BlkOp</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AB1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_OpEx</t>
+        </is>
+      </c>
+      <c r="AC1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_Str</t>
+        </is>
+      </c>
+      <c r="AD1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_DE_I</t>
+        </is>
+      </c>
+      <c r="AE1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_TPBRF_1_GENRBRF1_OpIn</t>
+        </is>
+      </c>
+      <c r="AF1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_GASSign</t>
+        </is>
+      </c>
+      <c r="AG1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_LowIsolGAS</t>
+        </is>
+      </c>
+      <c r="AH1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_GASBlock</t>
+        </is>
+      </c>
+      <c r="AI1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_TECHSign</t>
+        </is>
+      </c>
+      <c r="AJ1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_LowIsolTECH</t>
+        </is>
+      </c>
+      <c r="AK1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_TECHBlock</t>
+        </is>
+      </c>
+      <c r="AL1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_ALMSign</t>
+        </is>
+      </c>
+      <c r="AM1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_OpExt</t>
+        </is>
+      </c>
+      <c r="AN1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_CtlCir</t>
+        </is>
+      </c>
+      <c r="AO1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_TestBlock</t>
+        </is>
+      </c>
+      <c r="AP1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_OCSign</t>
+        </is>
+      </c>
+      <c r="AQ1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_GAS_OCControlSignAssem</t>
+        </is>
+      </c>
+      <c r="AR1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_TECH_OCControlSignAssem</t>
+        </is>
+      </c>
+      <c r="AS1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_OCnnSign</t>
+        </is>
+      </c>
+      <c r="AT1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_ExtSignGen</t>
+        </is>
+      </c>
+      <c r="AU1" s="4" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_Alarm</t>
         </is>
       </c>
     </row>
